--- a/CCA_ConfigSpecs.xlsx
+++ b/CCA_ConfigSpecs.xlsx
@@ -142,8 +142,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tbl_dataInputSpecs" displayName="Tbl_dataInputSpecs" ref="A1:G7" headerRowCount="1">
-  <autoFilter ref="A1:G7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tbl_dataInputSpecs" displayName="Tbl_dataInputSpecs" ref="A1:G8" headerRowCount="1">
+  <autoFilter ref="A1:G8"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Information"/>
     <tableColumn id="2" name="Sheet Name"/>
@@ -158,8 +158,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tbl_specDataFormats" displayName="Tbl_specDataFormats" ref="A1:E43" headerRowCount="1">
-  <autoFilter ref="A1:E43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tbl_specDataFormats" displayName="Tbl_specDataFormats" ref="A1:E55" headerRowCount="1">
+  <autoFilter ref="A1:E55"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Spec Table"/>
     <tableColumn id="2" name="Column"/>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -660,22 +660,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DataSources</t>
+          <t>SpecifyRuns</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dataset Name</t>
+          <t>Run Name</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -688,17 +688,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Subjects</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Subjects</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Subjects</t>
+          <t>DataSources</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dataset Name</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -711,17 +716,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Subjects</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Subjects</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>InuringLayers</t>
+          <t>Subjects</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -734,28 +739,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UpperLayers</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Layer</t>
+          <t>InuringLayers</t>
         </is>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>UpperLayers</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -773,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -923,32 +951,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dataset Name</t>
+          <t>Run Name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>Utf8</t>
         </is>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Source Type</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,138 +981,167 @@
           <t>Utf8</t>
         </is>
       </c>
-      <c r="E9" t="b">
+      <c r="D9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>File Path</t>
+          <t>Distortion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>Utf8</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>wang</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sheet</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>Utf8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>occurrence</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Table Name</t>
+          <t>Inuring Sharing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>Utf8</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>conditional</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Delimiter</t>
+          <t>Policy Split</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>Utf8</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>conditional</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Connection</t>
+          <t>Bounded Split</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>Utf8</t>
         </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Query</t>
+          <t>Clamp Negatives</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>Utf8</t>
         </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Sources</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Column Renames</t>
+          <t>Include Reinstatement Premium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>Utf8</t>
         </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Subjects</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Benchmark Comparison</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1095,36 +1149,39 @@
           <t>Utf8</t>
         </is>
       </c>
-      <c r="E17" t="b">
-        <v>1</v>
+      <c r="D17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Subjects</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LOBNAME</t>
+          <t>Grid Points</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Utf8</t>
-        </is>
+          <t>Float64</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Subjects</t>
+          <t>Specify Runs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Regions</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1136,34 +1193,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Subjects</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Dataset Name</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>Utf8</t>
         </is>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Source Type</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Float64</t>
+          <t>Utf8</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1173,152 +1233,131 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>File Path</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>Utf8</t>
         </is>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Float64</t>
-        </is>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
+          <t>Utf8</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Limit</t>
+          <t>Table Name</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Float64</t>
-        </is>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
+          <t>Utf8</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Delimiter</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Float64</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
+          <t>Utf8</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Connection</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>Utf8</t>
         </is>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Multiple Regions Per Policy</t>
+          <t>Query</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
+          <t>Utf8</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Inuring Layers</t>
+          <t>Data Sources</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Column Renames</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
+          <t>Utf8</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Subjects</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1333,72 +1372,63 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Subjects</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>LOBNAME</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Float64</t>
-        </is>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
+          <t>Utf8</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Subjects</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Limit</t>
+          <t>Regions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Float64</t>
-        </is>
-      </c>
-      <c r="E31" t="b">
-        <v>1</v>
+          <t>Utf8</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Subjects</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>Utf8</t>
         </is>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Stage</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1413,49 +1443,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Placement</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Float64</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
+          <t>Utf8</t>
+        </is>
+      </c>
+      <c r="E34" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Utf8</t>
-        </is>
+          <t>Float64</t>
+        </is>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Reinstatements</t>
+          <t>Limit</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1463,19 +1496,19 @@
           <t>Float64</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
+      <c r="E36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Reinstatement Rate</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1490,55 +1523,61 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Agg Limit</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Float64</t>
-        </is>
+          <t>Utf8</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Agg Deductible</t>
+          <t>Multiple Regions Per Policy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Float64</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
+          <t>Utf8</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Upper Layers</t>
+          <t>Inuring Layers</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Distortion</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>Utf8</t>
         </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1549,13 +1588,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Theta</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Float64</t>
-        </is>
+          <t>Utf8</t>
+        </is>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1566,15 +1608,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Multiple Regions Per Policy</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D42" t="b">
+          <t>Float64</t>
+        </is>
+      </c>
+      <c r="E42" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1586,15 +1628,243 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>Limit</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Float64</t>
+        </is>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Utf8</t>
+        </is>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Float64</t>
+        </is>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Float64</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Utf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reinstatements</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Float64</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Reinstatement Rate</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Float64</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agg Limit</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Float64</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Agg Deductible</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Float64</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Distortion</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Utf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Theta</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Float64</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Multiple Regions Per Policy</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Utf8</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Upper Layers</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D43" t="b">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Utf8</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
         <v>1</v>
       </c>
     </row>
